--- a/SGC-CKN/Excel/f1f9f324-bd97-442c-a8f8-84868d7f1b51_Thi_công_cọc_khoan_nhồi_P1-168_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/f1f9f324-bd97-442c-a8f8-84868d7f1b51_Thi_công_cọc_khoan_nhồi_P1-168_D800_02-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -166,18 +166,14 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">11:25
-02/04/2026</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">14:25
 02/04/2026</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:35
@@ -1366,13 +1362,13 @@
         <v>-39</v>
       </c>
       <c r="H17" s="25">
-        <v>1.42</v>
+        <v>4.42</v>
       </c>
       <c r="I17" s="25">
         <v>12.8</v>
       </c>
-      <c r="J17" s="8">
-        <v>9.04</v>
+      <c r="J17" s="15">
+        <v>2.9</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>29</v>
@@ -1389,10 +1385,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-39</v>
@@ -1415,7 +1411,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1521,31 +1517,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1742,13 +1738,13 @@
         <v>-39</v>
       </c>
       <c r="G8" s="25">
-        <v>1.42</v>
+        <v>4.42</v>
       </c>
       <c r="H8" s="25">
         <v>12.8</v>
       </c>
-      <c r="I8" s="8">
-        <v>9.04</v>
+      <c r="I8" s="15">
+        <v>2.9</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1782,7 +1778,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>29</v>
@@ -1800,13 +1796,13 @@
         <v>-44.19</v>
       </c>
       <c r="G10" s="33">
-        <v>7.83</v>
+        <v>10.83</v>
       </c>
       <c r="H10" s="33">
         <v>44.19</v>
       </c>
       <c r="I10" s="33">
-        <v>5.64</v>
+        <v>4.08</v>
       </c>
     </row>
   </sheetData>
